--- a/storage/assets/webc_excel/WEBC ELCO SEKADAU (START from KPB FEB 2024).xlsx
+++ b/storage/assets/webc_excel/WEBC ELCO SEKADAU (START from KPB FEB 2024).xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\h720s-itts01\H720_TS03_ARTEAMFS\KPB\PORTAL\WEBC MD START FROM AGUSTUS 2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE49D727-BDFD-4CBD-B53F-EC8376147F16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B3D13E2-5F2E-4904-B8CE-07DB806CCE07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="305">
   <si>
     <t>nama_region</t>
   </si>
@@ -938,6 +938,9 @@
   </si>
   <si>
     <t>TIDAK ADA KPB MEI 2026</t>
+  </si>
+  <si>
+    <t>TIDAK ADA KPB JUNI 2026</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1265,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R60"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -3393,6 +3396,11 @@
     <row r="60" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>303</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>304</v>
       </c>
     </row>
   </sheetData>
